--- a/public/template/template_import_surat_masuk.xlsx
+++ b/public/template/template_import_surat_masuk.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>DAFTAR SURAT MASUK</t>
   </si>
@@ -55,6 +55,18 @@
   </si>
   <si>
     <t>Test</t>
+  </si>
+  <si>
+    <t>Kepada</t>
+  </si>
+  <si>
+    <t>Ketua KPU Provinsi Bali</t>
+  </si>
+  <si>
+    <t>Undangan Rapat</t>
+  </si>
+  <si>
+    <t>KPU Kabupaten Badung</t>
   </si>
 </sst>
 </file>
@@ -151,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -168,15 +180,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,31 +498,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.42578125" customWidth="1"/>
+    <col min="5" max="5" width="40.42578125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="35" customWidth="1"/>
+    <col min="7" max="7" width="31.140625" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -520,51 +538,57 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="11">
         <v>2</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4">
       <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x12ac">
           <x12ac:list>Sub Bagian Umum dan Logistik,"Sub Bagian Partisipasi, Hubungan Masyarakat dan Sumber Daya Manusia",Sub Bagian Keuangan,"Sub Bagian Perencanaan, Data, dan Informasi",Sub Bagian Teknis Penyelenggaraan Pemilu,Sub Bagian Hukum</x12ac:list>
